--- a/data/Directorio.xlsx
+++ b/data/Directorio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80026105-CEB9-4787-83D7-DAF6004B39E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7C9422-F526-4730-B096-B32884FDF481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9C3DA27A-ACB8-4104-84AB-29150BB17655}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="87">
   <si>
     <t>CC</t>
   </si>
@@ -288,6 +288,18 @@
   </si>
   <si>
     <t>Tienda</t>
+  </si>
+  <si>
+    <t>Cafe</t>
+  </si>
+  <si>
+    <t>Drive_Thru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiosko </t>
+  </si>
+  <si>
+    <t>Tipo Tienda</t>
   </si>
 </sst>
 </file>
@@ -772,15 +784,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BEE886F-E84F-4BB3-AC4A-E5B9ACFCC02A}">
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="35.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -793,8 +806,11 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2">
         <v>38115</v>
       </c>
@@ -807,8 +823,11 @@
       <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="2">
         <v>38117</v>
       </c>
@@ -821,8 +840,11 @@
       <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="2">
         <v>38119</v>
       </c>
@@ -835,8 +857,11 @@
       <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="2">
         <v>38136</v>
       </c>
@@ -849,8 +874,11 @@
       <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="2">
         <v>38142</v>
       </c>
@@ -863,8 +891,11 @@
       <c r="D6" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="2">
         <v>38149</v>
       </c>
@@ -877,8 +908,11 @@
       <c r="D7" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="2">
         <v>38176</v>
       </c>
@@ -891,8 +925,11 @@
       <c r="D8" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="2">
         <v>38186</v>
       </c>
@@ -905,8 +942,11 @@
       <c r="D9" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="2">
         <v>38197</v>
       </c>
@@ -919,8 +959,11 @@
       <c r="D10" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="2">
         <v>38205</v>
       </c>
@@ -933,8 +976,11 @@
       <c r="D11" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="2">
         <v>38207</v>
       </c>
@@ -947,8 +993,11 @@
       <c r="D12" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="2">
         <v>38230</v>
       </c>
@@ -961,8 +1010,11 @@
       <c r="D13" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="2">
         <v>38266</v>
       </c>
@@ -975,8 +1027,11 @@
       <c r="D14" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="2">
         <v>38270</v>
       </c>
@@ -989,8 +1044,11 @@
       <c r="D15" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="2">
         <v>38333</v>
       </c>
@@ -1003,8 +1061,11 @@
       <c r="D16" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="2">
         <v>38339</v>
       </c>
@@ -1017,8 +1078,11 @@
       <c r="D17" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="2">
         <v>38363</v>
       </c>
@@ -1031,8 +1095,11 @@
       <c r="D18" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="2">
         <v>38368</v>
       </c>
@@ -1045,8 +1112,11 @@
       <c r="D19" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="2">
         <v>38371</v>
       </c>
@@ -1059,8 +1129,11 @@
       <c r="D20" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="2">
         <v>38374</v>
       </c>
@@ -1073,8 +1146,11 @@
       <c r="D21" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="2">
         <v>38394</v>
       </c>
@@ -1087,8 +1163,11 @@
       <c r="D22" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="2">
         <v>38401</v>
       </c>
@@ -1101,8 +1180,11 @@
       <c r="D23" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="2">
         <v>38411</v>
       </c>
@@ -1115,8 +1197,11 @@
       <c r="D24" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="2">
         <v>38427</v>
       </c>
@@ -1129,8 +1214,11 @@
       <c r="D25" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="2">
         <v>38431</v>
       </c>
@@ -1143,8 +1231,11 @@
       <c r="D26" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="2">
         <v>38442</v>
       </c>
@@ -1157,8 +1248,11 @@
       <c r="D27" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="2">
         <v>38456</v>
       </c>
@@ -1171,8 +1265,11 @@
       <c r="D28" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="2">
         <v>38458</v>
       </c>
@@ -1185,8 +1282,11 @@
       <c r="D29" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="2">
         <v>38460</v>
       </c>
@@ -1199,8 +1299,11 @@
       <c r="D30" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="2">
         <v>38475</v>
       </c>
@@ -1213,8 +1316,11 @@
       <c r="D31" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="2">
         <v>38507</v>
       </c>
@@ -1227,8 +1333,11 @@
       <c r="D32" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="2">
         <v>38515</v>
       </c>
@@ -1241,8 +1350,11 @@
       <c r="D33" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="2">
         <v>38527</v>
       </c>
@@ -1255,8 +1367,11 @@
       <c r="D34" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="2">
         <v>38529</v>
       </c>
@@ -1269,8 +1384,11 @@
       <c r="D35" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="2">
         <v>38535</v>
       </c>
@@ -1283,8 +1401,11 @@
       <c r="D36" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="2">
         <v>38546</v>
       </c>
@@ -1297,8 +1418,11 @@
       <c r="D37" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="2">
         <v>38561</v>
       </c>
@@ -1311,8 +1435,11 @@
       <c r="D38" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="2">
         <v>38590</v>
       </c>
@@ -1325,8 +1452,11 @@
       <c r="D39" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" s="2">
         <v>38604</v>
       </c>
@@ -1339,8 +1469,11 @@
       <c r="D40" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="E40" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" s="2">
         <v>38606</v>
       </c>
@@ -1353,8 +1486,11 @@
       <c r="D41" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="E41" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" s="2">
         <v>38651</v>
       </c>
@@ -1367,8 +1503,11 @@
       <c r="D42" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="E42" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" s="2">
         <v>38656</v>
       </c>
@@ -1381,8 +1520,11 @@
       <c r="D43" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="44" spans="1:4">
+      <c r="E43" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" s="2">
         <v>38661</v>
       </c>
@@ -1395,8 +1537,11 @@
       <c r="D44" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="E44" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" s="2">
         <v>38674</v>
       </c>
@@ -1409,8 +1554,11 @@
       <c r="D45" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="1:4">
+      <c r="E45" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" s="2">
         <v>38677</v>
       </c>
@@ -1423,8 +1571,11 @@
       <c r="D46" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="E46" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" s="2">
         <v>38694</v>
       </c>
@@ -1437,8 +1588,11 @@
       <c r="D47" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="1:4">
+      <c r="E47" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" s="2">
         <v>38695</v>
       </c>
@@ -1451,8 +1605,11 @@
       <c r="D48" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
+      <c r="E48" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" s="2">
         <v>38719</v>
       </c>
@@ -1465,8 +1622,11 @@
       <c r="D49" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="50" spans="1:4">
+      <c r="E49" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" s="2">
         <v>38770</v>
       </c>
@@ -1479,8 +1639,11 @@
       <c r="D50" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
+      <c r="E50" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" s="2">
         <v>38792</v>
       </c>
@@ -1493,8 +1656,11 @@
       <c r="D51" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="E51" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" s="2">
         <v>38811</v>
       </c>
@@ -1507,8 +1673,11 @@
       <c r="D52" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="53" spans="1:4">
+      <c r="E52" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" s="2">
         <v>38837</v>
       </c>
@@ -1521,8 +1690,11 @@
       <c r="D53" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="E53" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" s="2">
         <v>38845</v>
       </c>
@@ -1535,8 +1707,11 @@
       <c r="D54" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="1:4">
+      <c r="E54" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" s="2">
         <v>38859</v>
       </c>
@@ -1549,8 +1724,11 @@
       <c r="D55" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="56" spans="1:4">
+      <c r="E55" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" s="2">
         <v>38862</v>
       </c>
@@ -1563,8 +1741,11 @@
       <c r="D56" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="57" spans="1:4">
+      <c r="E56" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" s="2">
         <v>38894</v>
       </c>
@@ -1577,8 +1758,11 @@
       <c r="D57" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="58" spans="1:4">
+      <c r="E57" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" s="2">
         <v>38903</v>
       </c>
@@ -1591,8 +1775,11 @@
       <c r="D58" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="59" spans="1:4">
+      <c r="E58" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" s="2">
         <v>38924</v>
       </c>
@@ -1605,8 +1792,11 @@
       <c r="D59" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="E59" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" s="2">
         <v>38925</v>
       </c>
@@ -1619,8 +1809,11 @@
       <c r="D60" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="1:4">
+      <c r="E60" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" s="2">
         <v>38930</v>
       </c>
@@ -1633,8 +1826,11 @@
       <c r="D61" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="E61" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" s="2">
         <v>38937</v>
       </c>
@@ -1647,8 +1843,11 @@
       <c r="D62" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="E62" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" s="2">
         <v>38965</v>
       </c>
@@ -1661,8 +1860,11 @@
       <c r="D63" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="64" spans="1:4">
+      <c r="E63" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" s="2">
         <v>38992</v>
       </c>
@@ -1675,8 +1877,11 @@
       <c r="D64" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="65" spans="1:4">
+      <c r="E64" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" s="2">
         <v>38995</v>
       </c>
@@ -1689,8 +1894,11 @@
       <c r="D65" s="4" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="66" spans="1:4">
+      <c r="E65" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" s="2">
         <v>43043</v>
       </c>
@@ -1703,8 +1911,11 @@
       <c r="D66" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="1:4">
+      <c r="E66" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" s="2">
         <v>43111</v>
       </c>
@@ -1717,8 +1928,11 @@
       <c r="D67" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="68" spans="1:4">
+      <c r="E67" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" s="2">
         <v>43130</v>
       </c>
@@ -1731,8 +1945,11 @@
       <c r="D68" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="69" spans="1:4">
+      <c r="E68" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" s="2">
         <v>43132</v>
       </c>
@@ -1745,8 +1962,11 @@
       <c r="D69" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="70" spans="1:4">
+      <c r="E69" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" s="2">
         <v>43152</v>
       </c>
@@ -1759,8 +1979,11 @@
       <c r="D70" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="71" spans="1:4">
+      <c r="E70" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" s="2">
         <v>43193</v>
       </c>
@@ -1773,8 +1996,11 @@
       <c r="D71" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="72" spans="1:4">
+      <c r="E71" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" s="2">
         <v>43194</v>
       </c>
@@ -1787,8 +2013,11 @@
       <c r="D72" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="73" spans="1:4">
+      <c r="E72" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" s="2">
         <v>43195</v>
       </c>
@@ -1801,27 +2030,22 @@
       <c r="D73" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="E73" s="4" t="s">
+        <v>85</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A73">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A73">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A73">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A73">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A73">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A73">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
